--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="605">
   <si>
     <t>男</t>
   </si>
@@ -2225,6 +2225,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（演</t>
     </r>
     <r>
@@ -2242,6 +2248,12 @@
   </si>
   <si>
     <t>しょくみんしゃ</t>
+  </si>
+  <si>
+    <t>名探偵</t>
+  </si>
+  <si>
+    <t>めいたんてい</t>
   </si>
   <si>
     <t>裏切り者</t>
@@ -2401,7 +2413,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2432,13 +2444,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2907,28 +2912,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2937,118 +2945,115 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5421,51 +5426,57 @@
       </c>
     </row>
     <row r="32" spans="4:18">
+      <c r="D32" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="N32" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="33" spans="14:16">
       <c r="P33" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="34" spans="14:16">
       <c r="N34" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="35" spans="14:16">
       <c r="N35" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36" spans="14:16">
       <c r="N36" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="37" spans="14:16">
       <c r="N37" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="39" spans="14:16">
@@ -5478,7 +5489,7 @@
     </row>
     <row r="40" spans="14:16">
       <c r="N40" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>463</v>
@@ -5486,29 +5497,29 @@
     </row>
     <row r="41" spans="14:16">
       <c r="N41" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="42" spans="14:16">
       <c r="N42" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="44" spans="14:16">
       <c r="N44" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="45" spans="14:16">
@@ -5529,53 +5540,53 @@
     </row>
     <row r="48" spans="14:16">
       <c r="N48" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="14:16">
       <c r="N49" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="50" spans="14:16">
       <c r="N50" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" spans="14:16">
       <c r="N51" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="52" spans="14:16">
       <c r="N52" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="53" spans="14:16">
       <c r="N53" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -5595,64 +5606,64 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="619">
   <si>
     <t>男</t>
   </si>
@@ -502,31 +502,61 @@
     <t>特殊（とくしゅ）</t>
   </si>
   <si>
+    <t>所帯</t>
+  </si>
+  <si>
+    <t>しょたい</t>
+  </si>
+  <si>
+    <t>（家庭，户口）</t>
+  </si>
+  <si>
+    <t>奥さん</t>
+  </si>
+  <si>
+    <t>おくさん</t>
+  </si>
+  <si>
+    <t>（人妻尊称）</t>
+  </si>
+  <si>
+    <t>友達</t>
+  </si>
+  <si>
+    <t>ともだち</t>
+  </si>
+  <si>
+    <t>尊敬</t>
+  </si>
+  <si>
+    <t>そんけい</t>
+  </si>
+  <si>
     <t>父母</t>
   </si>
   <si>
     <t>ふぼ</t>
   </si>
   <si>
-    <t>奥さん</t>
-  </si>
-  <si>
-    <t>おくさん</t>
-  </si>
-  <si>
-    <t>（人妻尊称）</t>
-  </si>
-  <si>
-    <t>友達</t>
-  </si>
-  <si>
-    <t>ともだち</t>
-  </si>
-  <si>
-    <t>尊敬</t>
-  </si>
-  <si>
-    <t>そんけい</t>
+    <t>女房</t>
+  </si>
+  <si>
+    <t>にょうぼう</t>
+  </si>
+  <si>
+    <t>（人妻）</t>
+  </si>
+  <si>
+    <t>友人</t>
+  </si>
+  <si>
+    <t>ゆうじん</t>
+  </si>
+  <si>
+    <t>似る</t>
+  </si>
+  <si>
+    <t>にる</t>
   </si>
   <si>
     <t>父親</t>
@@ -535,49 +565,22 @@
     <t>ちちおや</t>
   </si>
   <si>
-    <t>女房</t>
-  </si>
-  <si>
-    <t>にょうぼう</t>
-  </si>
-  <si>
-    <t>（人妻）</t>
-  </si>
-  <si>
-    <t>友人</t>
-  </si>
-  <si>
-    <t>ゆうじん</t>
-  </si>
-  <si>
-    <t>似る</t>
-  </si>
-  <si>
-    <t>にる</t>
+    <t>顧客</t>
+  </si>
+  <si>
+    <t>こきゃく</t>
+  </si>
+  <si>
+    <t>同僚</t>
+  </si>
+  <si>
+    <t>どうりょう</t>
   </si>
   <si>
     <t>母親</t>
   </si>
   <si>
     <t>ははおや</t>
-  </si>
-  <si>
-    <t>顧客</t>
-  </si>
-  <si>
-    <t>こきゃく</t>
-  </si>
-  <si>
-    <t>同僚</t>
-  </si>
-  <si>
-    <t>どうりょう</t>
-  </si>
-  <si>
-    <t>夫妻</t>
-  </si>
-  <si>
-    <t>ふさい</t>
   </si>
   <si>
     <t>得意先</t>
@@ -621,22 +624,31 @@
     <t>こい</t>
   </si>
   <si>
+    <t>夫妻</t>
+  </si>
+  <si>
+    <t>ふさい</t>
+  </si>
+  <si>
+    <t>被害者</t>
+  </si>
+  <si>
+    <t>ひがいしゃ</t>
+  </si>
+  <si>
+    <t>仲間</t>
+  </si>
+  <si>
+    <t>なかま</t>
+  </si>
+  <si>
     <t>夫婦</t>
   </si>
   <si>
     <t>ふうふ</t>
   </si>
   <si>
-    <t>被害者</t>
-  </si>
-  <si>
-    <t>ひがいしゃ</t>
-  </si>
-  <si>
-    <t>仲間</t>
-  </si>
-  <si>
-    <t>なかま</t>
+    <t>（对方）</t>
   </si>
   <si>
     <t>親子</t>
@@ -645,19 +657,25 @@
     <t>おやこ</t>
   </si>
   <si>
+    <t>（女儿）</t>
+  </si>
+  <si>
+    <t>お母さん</t>
+  </si>
+  <si>
+    <t>おかあさん</t>
+  </si>
+  <si>
     <t>娘</t>
   </si>
   <si>
     <t>むすめ</t>
   </si>
   <si>
-    <t>（女儿）</t>
-  </si>
-  <si>
-    <t>お母さん</t>
-  </si>
-  <si>
-    <t>おかあさん</t>
+    <t>お父さん</t>
+  </si>
+  <si>
+    <t>おとうさん</t>
   </si>
   <si>
     <t>長女</t>
@@ -666,10 +684,13 @@
     <t>ちょうじょ</t>
   </si>
   <si>
-    <t>お父さん</t>
-  </si>
-  <si>
-    <t>おとうさん</t>
+    <t>息子</t>
+  </si>
+  <si>
+    <t>むすこ</t>
+  </si>
+  <si>
+    <t>（儿子）</t>
   </si>
   <si>
     <t>次女</t>
@@ -678,34 +699,19 @@
     <t>じじょ</t>
   </si>
   <si>
-    <t>息子</t>
-  </si>
-  <si>
-    <t>むすこ</t>
-  </si>
-  <si>
-    <t>（儿子）</t>
+    <t>子供</t>
+  </si>
+  <si>
+    <t>こども</t>
+  </si>
+  <si>
+    <t>（自家小孩）</t>
   </si>
   <si>
     <t>三女</t>
   </si>
   <si>
     <t>さんじょ</t>
-  </si>
-  <si>
-    <t>子供</t>
-  </si>
-  <si>
-    <t>こども</t>
-  </si>
-  <si>
-    <t>（自家小孩）</t>
-  </si>
-  <si>
-    <t>末っ子</t>
-  </si>
-  <si>
-    <t>すえっこ</t>
   </si>
   <si>
     <t>お子さん</t>
@@ -743,16 +749,28 @@
     </r>
   </si>
   <si>
+    <t>末っ子</t>
+  </si>
+  <si>
+    <t>すえっこ</t>
+  </si>
+  <si>
+    <t>兄さん</t>
+  </si>
+  <si>
+    <t>あにさん</t>
+  </si>
+  <si>
     <t>姐、姉</t>
   </si>
   <si>
     <t>あね</t>
   </si>
   <si>
-    <t>兄さん</t>
-  </si>
-  <si>
-    <t>あにさん</t>
+    <t>お兄さん</t>
+  </si>
+  <si>
+    <t>おにいさん</t>
   </si>
   <si>
     <t>妹</t>
@@ -761,10 +779,10 @@
     <t>いもうと</t>
   </si>
   <si>
-    <t>お兄さん</t>
-  </si>
-  <si>
-    <t>おにいさん</t>
+    <t>両親</t>
+  </si>
+  <si>
+    <t>りょうおや</t>
   </si>
   <si>
     <t>姉妹</t>
@@ -773,10 +791,10 @@
     <t>しまい</t>
   </si>
   <si>
-    <t>両親</t>
-  </si>
-  <si>
-    <t>りょうおや</t>
+    <t>直系尊属</t>
+  </si>
+  <si>
+    <t>ちょっけいそんぞく</t>
   </si>
   <si>
     <t>兄弟</t>
@@ -785,10 +803,13 @@
     <t>きょうだい</t>
   </si>
   <si>
-    <t>直系尊属</t>
-  </si>
-  <si>
-    <t>ちょっけいそんぞく</t>
+    <t>留守番</t>
+  </si>
+  <si>
+    <t>るすばん</t>
+  </si>
+  <si>
+    <t>（看家人）</t>
   </si>
   <si>
     <t>兄</t>
@@ -797,13 +818,10 @@
     <t>あに</t>
   </si>
   <si>
-    <t>留守番</t>
-  </si>
-  <si>
-    <t>るすばん</t>
-  </si>
-  <si>
-    <t>（看家人）</t>
+    <t>老人</t>
+  </si>
+  <si>
+    <t>ろうじん</t>
   </si>
   <si>
     <t>弟</t>
@@ -812,10 +830,13 @@
     <t>おとうと</t>
   </si>
   <si>
-    <t>老人</t>
-  </si>
-  <si>
-    <t>ろうじん</t>
+    <t>お年寄り</t>
+  </si>
+  <si>
+    <t>おとしより</t>
+  </si>
+  <si>
+    <t>（老人）</t>
   </si>
   <si>
     <t>長男</t>
@@ -824,13 +845,13 @@
     <t>ちょうなん</t>
   </si>
   <si>
-    <t>お年寄り</t>
-  </si>
-  <si>
-    <t>おとしより</t>
-  </si>
-  <si>
-    <t>（老人）</t>
+    <t>（独生子女）</t>
+  </si>
+  <si>
+    <t>年配</t>
+  </si>
+  <si>
+    <t>ねんぱい</t>
   </si>
   <si>
     <t>次男</t>
@@ -839,34 +860,19 @@
     <t>じなん</t>
   </si>
   <si>
-    <t>（独生子女）</t>
-  </si>
-  <si>
-    <t>年配</t>
-  </si>
-  <si>
-    <t>ねんぱい</t>
+    <t>老若男女</t>
+  </si>
+  <si>
+    <t>ろうにゃくなんにょ</t>
+  </si>
+  <si>
+    <t>（男女老少）</t>
   </si>
   <si>
     <t>三男</t>
   </si>
   <si>
     <t>さんなん</t>
-  </si>
-  <si>
-    <t>老若男女</t>
-  </si>
-  <si>
-    <t>ろうにゃくなんにょ</t>
-  </si>
-  <si>
-    <t>（男女老少）</t>
-  </si>
-  <si>
-    <t>一人っ子</t>
-  </si>
-  <si>
-    <t>ひとりっこ</t>
   </si>
   <si>
     <t>（爷爷）</t>
@@ -907,10 +913,10 @@
     </r>
   </si>
   <si>
-    <t>叔母、伯母</t>
-  </si>
-  <si>
-    <t>おば</t>
+    <t>一人っ子</t>
+  </si>
+  <si>
+    <t>ひとりっこ</t>
   </si>
   <si>
     <t>（奶奶）</t>
@@ -951,19 +957,34 @@
     </r>
   </si>
   <si>
+    <t>叔母、伯母</t>
+  </si>
+  <si>
+    <t>おば</t>
+  </si>
+  <si>
+    <t>荷受人</t>
+  </si>
+  <si>
+    <t>にうけにん</t>
+  </si>
+  <si>
+    <t>（收货人）</t>
+  </si>
+  <si>
     <t>叔父、伯父</t>
   </si>
   <si>
     <t>おじ</t>
   </si>
   <si>
-    <t>荷受人</t>
-  </si>
-  <si>
-    <t>にうけにん</t>
-  </si>
-  <si>
-    <t>（收货人）</t>
+    <t>同士</t>
+  </si>
+  <si>
+    <t>どうし</t>
+  </si>
+  <si>
+    <t>（同志）</t>
   </si>
   <si>
     <t>姥、伯母</t>
@@ -972,31 +993,16 @@
     <t>うば</t>
   </si>
   <si>
-    <t>同士</t>
-  </si>
-  <si>
-    <t>どうし</t>
-  </si>
-  <si>
-    <t>（同志）</t>
+    <t>同胞</t>
+  </si>
+  <si>
+    <t>どうほう</t>
   </si>
   <si>
     <t>爺</t>
   </si>
   <si>
     <t>じじい</t>
-  </si>
-  <si>
-    <t>同胞</t>
-  </si>
-  <si>
-    <t>どうほう</t>
-  </si>
-  <si>
-    <t>お爺さん</t>
-  </si>
-  <si>
-    <t>おじいさん</t>
   </si>
   <si>
     <t>酔っ払い</t>
@@ -1034,40 +1040,40 @@
     </r>
   </si>
   <si>
+    <t>お爺さん</t>
+  </si>
+  <si>
+    <t>おじいさん</t>
+  </si>
+  <si>
+    <t>近所</t>
+  </si>
+  <si>
+    <t>きんじょ</t>
+  </si>
+  <si>
+    <t>（隣）</t>
+  </si>
+  <si>
     <t>祖母</t>
   </si>
   <si>
     <t>そぼ</t>
   </si>
   <si>
-    <t>近所</t>
-  </si>
-  <si>
-    <t>きんじょ</t>
-  </si>
-  <si>
-    <t>（隣）</t>
+    <t>（外甥）</t>
+  </si>
+  <si>
+    <t>集団生活</t>
+  </si>
+  <si>
+    <t>しゅうだんせいかつ</t>
   </si>
   <si>
     <t>従兄弟、従姉妹</t>
   </si>
   <si>
     <t>いとこ</t>
-  </si>
-  <si>
-    <t>（外甥）</t>
-  </si>
-  <si>
-    <t>集団生活</t>
-  </si>
-  <si>
-    <t>しゅうだんせいかつ</t>
-  </si>
-  <si>
-    <t>甥</t>
-  </si>
-  <si>
-    <t>おい</t>
   </si>
   <si>
     <r>
@@ -1091,6 +1097,18 @@
     </r>
   </si>
   <si>
+    <t>連合組合</t>
+  </si>
+  <si>
+    <t>れんごうくみあい</t>
+  </si>
+  <si>
+    <t>甥</t>
+  </si>
+  <si>
+    <t>おい</t>
+  </si>
+  <si>
     <t>姪</t>
   </si>
   <si>
@@ -1101,12 +1119,6 @@
   </si>
   <si>
     <t>まご</t>
-  </si>
-  <si>
-    <t>隣</t>
-  </si>
-  <si>
-    <t>となり</t>
   </si>
   <si>
     <r>
@@ -1138,43 +1150,58 @@
     </r>
   </si>
   <si>
+    <t>隣</t>
+  </si>
+  <si>
+    <t>となり</t>
+  </si>
+  <si>
+    <t>（亲戚）</t>
+  </si>
+  <si>
     <t>親戚</t>
   </si>
   <si>
     <t>しんせき</t>
   </si>
   <si>
-    <t>（亲戚）</t>
-  </si>
-  <si>
     <t>親類</t>
   </si>
   <si>
     <t>しんるい</t>
   </si>
   <si>
+    <t>（寡妇）</t>
+  </si>
+  <si>
     <t>未亡人</t>
   </si>
   <si>
     <t>みぼうじん</t>
   </si>
   <si>
-    <t>（寡妇）</t>
-  </si>
-  <si>
     <t>先祖</t>
   </si>
   <si>
     <t>せんぞ</t>
   </si>
   <si>
+    <t>（双胞胎）</t>
+  </si>
+  <si>
     <t>双子</t>
   </si>
   <si>
     <t>ふたご</t>
   </si>
   <si>
-    <t>（双胞胎）</t>
+    <t>坊や</t>
+  </si>
+  <si>
+    <t>ぼうや</t>
+  </si>
+  <si>
+    <t>（毛头小子）</t>
   </si>
   <si>
     <t>教育｜きょういく</t>
@@ -2144,16 +2171,10 @@
     </r>
   </si>
   <si>
-    <t>追放者</t>
-  </si>
-  <si>
-    <t>ついほうしゃ</t>
-  </si>
-  <si>
-    <t>専門家</t>
-  </si>
-  <si>
-    <t>せんもんか</t>
+    <t>当番</t>
+  </si>
+  <si>
+    <t>とうばん</t>
   </si>
   <si>
     <r>
@@ -2169,6 +2190,47 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>班人）</t>
+    </r>
+  </si>
+  <si>
+    <t>追放者</t>
+  </si>
+  <si>
+    <t>ついほうしゃ</t>
+  </si>
+  <si>
+    <t>専門家</t>
+  </si>
+  <si>
+    <t>せんもんか</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
@@ -2353,6 +2415,12 @@
   </si>
   <si>
     <t>みょうじょう</t>
+  </si>
+  <si>
+    <t>観客</t>
+  </si>
+  <si>
+    <t>かんきゃく</t>
   </si>
   <si>
     <t>株式会社</t>
@@ -2599,14 +2667,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3897,7 +3965,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22.6666666666667" customWidth="1"/>
@@ -3922,585 +3990,622 @@
       <c r="A2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>120</v>
       </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J3" s="1"/>
       <c r="L3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" t="s">
         <v>138</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="D4" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>203</v>
+      <c r="A18" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>207</v>
+      <c r="A19" t="s">
+        <v>209</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F21" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
+      </c>
+      <c r="D30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C34" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>283</v>
-      </c>
-      <c r="B38" t="s">
-        <v>284</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" ht="18" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="C38" t="s">
-        <v>285</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>292</v>
+      </c>
+      <c r="B40" t="s">
+        <v>293</v>
+      </c>
+      <c r="C40" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4512,7 +4617,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -4534,1059 +4639,1076 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="D12" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="D13" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="D14" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="D15" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="D16" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" spans="4:18">
       <c r="D17" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="4:18">
       <c r="D18" s="1" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="4:18">
       <c r="D19" s="1" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="4:18">
       <c r="D20" s="1" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="4:18">
       <c r="D21" s="1" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="4:18">
       <c r="D22" s="1" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="4:18">
       <c r="D23" s="1" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="24" spans="4:18">
       <c r="D24" s="1" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="25" spans="4:18">
       <c r="D25" s="1" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
     </row>
     <row r="26" spans="4:18">
       <c r="D26" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>529</v>
+        <v>538</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>541</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="27" spans="4:18">
       <c r="D27" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28" spans="4:18">
       <c r="D28" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="4:18">
       <c r="D29" s="1" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
     </row>
     <row r="30" spans="4:18">
       <c r="D30" s="1" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31" spans="4:18">
       <c r="D31" s="1" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="32" spans="4:18">
       <c r="D32" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
     </row>
     <row r="33" spans="14:16">
       <c r="P33" s="3" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
     </row>
     <row r="34" spans="14:16">
       <c r="N34" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35" spans="14:16">
       <c r="N35" s="1" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
     </row>
     <row r="36" spans="14:16">
       <c r="N36" s="1" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="37" spans="14:16">
       <c r="N37" s="1" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="14:16">
       <c r="N39" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="14:16">
       <c r="N40" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" spans="14:16">
       <c r="N41" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="42" spans="14:16">
       <c r="N42" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
     </row>
     <row r="44" spans="14:16">
       <c r="N44" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
     </row>
     <row r="45" spans="14:16">
       <c r="N45" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" spans="14:16">
       <c r="N46" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" spans="14:16">
       <c r="N48" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
     </row>
     <row r="49" spans="14:16">
       <c r="N49" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="50" spans="14:16">
       <c r="N50" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="51" spans="14:16">
       <c r="N51" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
     </row>
     <row r="52" spans="14:16">
       <c r="N52" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
     <row r="53" spans="14:16">
       <c r="N53" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>588</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="14:16">
+      <c r="N54" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -5606,64 +5728,64 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="5" activeTab="5"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="5" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="人（ひと）" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="624">
   <si>
     <t>男</t>
   </si>
@@ -818,16 +818,40 @@
     <t>あに</t>
   </si>
   <si>
+    <t>青年</t>
+  </si>
+  <si>
+    <t>せいねん</t>
+  </si>
+  <si>
+    <t>弟</t>
+  </si>
+  <si>
+    <t>おとうと</t>
+  </si>
+  <si>
+    <t>成年</t>
+  </si>
+  <si>
+    <t>長男</t>
+  </si>
+  <si>
+    <t>ちょうなん</t>
+  </si>
+  <si>
+    <t>（独生子女）</t>
+  </si>
+  <si>
     <t>老人</t>
   </si>
   <si>
     <t>ろうじん</t>
   </si>
   <si>
-    <t>弟</t>
-  </si>
-  <si>
-    <t>おとうと</t>
+    <t>次男</t>
+  </si>
+  <si>
+    <t>じなん</t>
   </si>
   <si>
     <t>お年寄り</t>
@@ -839,13 +863,13 @@
     <t>（老人）</t>
   </si>
   <si>
-    <t>長男</t>
-  </si>
-  <si>
-    <t>ちょうなん</t>
-  </si>
-  <si>
-    <t>（独生子女）</t>
+    <t>三男</t>
+  </si>
+  <si>
+    <t>さんなん</t>
+  </si>
+  <si>
+    <t>（爷爷）</t>
   </si>
   <si>
     <t>年配</t>
@@ -854,10 +878,13 @@
     <t>ねんぱい</t>
   </si>
   <si>
-    <t>次男</t>
-  </si>
-  <si>
-    <t>じなん</t>
+    <t>一人っ子</t>
+  </si>
+  <si>
+    <t>ひとりっこ</t>
+  </si>
+  <si>
+    <t>（奶奶）</t>
   </si>
   <si>
     <t>老若男女</t>
@@ -869,13 +896,10 @@
     <t>（男女老少）</t>
   </si>
   <si>
-    <t>三男</t>
-  </si>
-  <si>
-    <t>さんなん</t>
-  </si>
-  <si>
-    <t>（爷爷）</t>
+    <t>叔母、伯母</t>
+  </si>
+  <si>
+    <t>おば</t>
   </si>
   <si>
     <t>目上の人</t>
@@ -913,13 +937,10 @@
     </r>
   </si>
   <si>
-    <t>一人っ子</t>
-  </si>
-  <si>
-    <t>ひとりっこ</t>
-  </si>
-  <si>
-    <t>（奶奶）</t>
+    <t>叔父、伯父</t>
+  </si>
+  <si>
+    <t>おじ</t>
   </si>
   <si>
     <t>差出人</t>
@@ -957,10 +978,10 @@
     </r>
   </si>
   <si>
-    <t>叔母、伯母</t>
-  </si>
-  <si>
-    <t>おば</t>
+    <t>姥、伯母</t>
+  </si>
+  <si>
+    <t>うば</t>
   </si>
   <si>
     <t>荷受人</t>
@@ -972,10 +993,10 @@
     <t>（收货人）</t>
   </si>
   <si>
-    <t>叔父、伯父</t>
-  </si>
-  <si>
-    <t>おじ</t>
+    <t>爺</t>
+  </si>
+  <si>
+    <t>じじい</t>
   </si>
   <si>
     <t>同士</t>
@@ -987,10 +1008,10 @@
     <t>（同志）</t>
   </si>
   <si>
-    <t>姥、伯母</t>
-  </si>
-  <si>
-    <t>うば</t>
+    <t>お爺さん</t>
+  </si>
+  <si>
+    <t>おじいさん</t>
   </si>
   <si>
     <t>同胞</t>
@@ -999,10 +1020,13 @@
     <t>どうほう</t>
   </si>
   <si>
-    <t>爺</t>
-  </si>
-  <si>
-    <t>じじい</t>
+    <t>祖母</t>
+  </si>
+  <si>
+    <t>そぼ</t>
+  </si>
+  <si>
+    <t>（外甥）</t>
   </si>
   <si>
     <t>酔っ払い</t>
@@ -1038,36 +1062,6 @@
       </rPr>
       <t>）</t>
     </r>
-  </si>
-  <si>
-    <t>お爺さん</t>
-  </si>
-  <si>
-    <t>おじいさん</t>
-  </si>
-  <si>
-    <t>近所</t>
-  </si>
-  <si>
-    <t>きんじょ</t>
-  </si>
-  <si>
-    <t>（隣）</t>
-  </si>
-  <si>
-    <t>祖母</t>
-  </si>
-  <si>
-    <t>そぼ</t>
-  </si>
-  <si>
-    <t>（外甥）</t>
-  </si>
-  <si>
-    <t>集団生活</t>
-  </si>
-  <si>
-    <t>しゅうだんせいかつ</t>
   </si>
   <si>
     <t>従兄弟、従姉妹</t>
@@ -1097,22 +1091,37 @@
     </r>
   </si>
   <si>
+    <t>近所</t>
+  </si>
+  <si>
+    <t>きんじょ</t>
+  </si>
+  <si>
+    <t>（隣）</t>
+  </si>
+  <si>
+    <t>甥</t>
+  </si>
+  <si>
+    <t>おい</t>
+  </si>
+  <si>
+    <t>集団生活</t>
+  </si>
+  <si>
+    <t>しゅうだんせいかつ</t>
+  </si>
+  <si>
+    <t>姪</t>
+  </si>
+  <si>
+    <t>めい</t>
+  </si>
+  <si>
     <t>連合組合</t>
   </si>
   <si>
     <t>れんごうくみあい</t>
-  </si>
-  <si>
-    <t>甥</t>
-  </si>
-  <si>
-    <t>おい</t>
-  </si>
-  <si>
-    <t>姪</t>
-  </si>
-  <si>
-    <t>めい</t>
   </si>
   <si>
     <t>孫</t>
@@ -2325,6 +2334,12 @@
   </si>
   <si>
     <t>诈骗犯</t>
+  </si>
+  <si>
+    <t>冒険者</t>
+  </si>
+  <si>
+    <t>ぼうけんしゃ</t>
   </si>
   <si>
     <t>虞犯</t>
@@ -4290,10 +4305,10 @@
       <c r="B18" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4304,308 +4319,320 @@
       <c r="B19" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>211</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>213</v>
+      <c r="E19" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
       <c r="A21" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="E21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F21" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:6">
       <c r="A22" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" t="s">
         <v>224</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D22" t="s">
-        <v>227</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:6">
       <c r="A23" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E23" t="s">
         <v>231</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>232</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:6">
       <c r="A24" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F24" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:6">
       <c r="A25" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:6">
       <c r="A26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="F26" t="s">
         <v>247</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:6">
       <c r="A27" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:6">
       <c r="A28" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:6">
       <c r="A29" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E30" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:6">
       <c r="A31" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>271</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
+      </c>
+      <c r="D32" t="s">
+        <v>275</v>
+      </c>
+      <c r="E32" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C34" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C38" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4617,7 +4644,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -4639,1076 +4666,1082 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="D12" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="D13" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="D14" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="D15" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="D16" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="R16" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" spans="4:18">
       <c r="D17" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" spans="4:18">
       <c r="D18" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="4:18">
       <c r="D19" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="4:18">
       <c r="D20" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="4:18">
       <c r="D21" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="4:18">
       <c r="D22" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="4:18">
       <c r="D23" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="4:18">
       <c r="D24" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="25" spans="4:18">
       <c r="D25" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="26" spans="4:18">
       <c r="D26" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27" spans="4:18">
       <c r="D27" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" spans="4:18">
       <c r="D28" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="29" spans="4:18">
       <c r="D29" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="30" spans="4:18">
       <c r="D30" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="4:18">
       <c r="D31" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="32" spans="4:18">
       <c r="D32" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="33" spans="14:16">
-      <c r="P33" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="34" spans="14:16">
-      <c r="N34" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>573</v>
+      <c r="N33" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="35" spans="14:16">
       <c r="N35" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="36" spans="14:16">
       <c r="N36" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="37" spans="14:16">
       <c r="N37" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="39" spans="14:16">
-      <c r="N39" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>472</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="38" spans="14:16">
+      <c r="N38" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="40" spans="14:16">
       <c r="N40" s="1" t="s">
-        <v>580</v>
+        <v>474</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="41" spans="14:16">
       <c r="N41" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>583</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" spans="14:16">
       <c r="N42" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="44" spans="14:16">
-      <c r="N44" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="O44" s="1" t="s">
         <v>587</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="43" spans="14:16">
+      <c r="N43" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="45" spans="14:16">
       <c r="N45" s="1" t="s">
-        <v>396</v>
+        <v>591</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>397</v>
+        <v>592</v>
       </c>
     </row>
     <row r="46" spans="14:16">
       <c r="N46" s="1" t="s">
-        <v>442</v>
+        <v>399</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="48" spans="14:16">
-      <c r="N48" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>589</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="14:16">
+      <c r="N47" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="14:16">
       <c r="N49" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="50" spans="14:16">
       <c r="N50" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="51" spans="14:16">
       <c r="N51" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="52" spans="14:16">
       <c r="N52" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="14:16">
       <c r="N53" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="54" spans="14:16">
       <c r="N54" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="55" spans="14:16">
+      <c r="N55" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -5728,64 +5761,64 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="5" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="5" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="人（ひと）" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="629">
   <si>
     <t>男</t>
   </si>
@@ -678,6 +678,12 @@
     <t>おとうさん</t>
   </si>
   <si>
+    <t>噓つき</t>
+  </si>
+  <si>
+    <t>（喜欢说谎的人）</t>
+  </si>
+  <si>
     <t>長女</t>
   </si>
   <si>
@@ -2333,13 +2339,42 @@
     <t>うらぎりもの</t>
   </si>
   <si>
-    <t>诈骗犯</t>
+    <t>（诈骗犯）</t>
   </si>
   <si>
     <t>冒険者</t>
   </si>
   <si>
     <t>ぼうけんしゃ</t>
+  </si>
+  <si>
+    <t>負傷者</t>
+  </si>
+  <si>
+    <t>ふしょうしゃ</t>
+  </si>
+  <si>
+    <r>
+      <t>（受</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>者）</t>
+    </r>
   </si>
   <si>
     <t>虞犯</t>
@@ -2676,14 +2711,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4159,6 +4194,15 @@
       <c r="E8" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="1" t="s">
@@ -4173,466 +4217,475 @@
       <c r="E9" s="1" t="s">
         <v>168</v>
       </c>
+      <c r="H9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:6">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" t="s">
         <v>210</v>
-      </c>
-      <c r="D19" t="s">
-        <v>211</v>
-      </c>
-      <c r="E19" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C22" t="s">
-        <v>224</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D32" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C34" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C35" t="s">
         <v>284</v>
-      </c>
-      <c r="C35" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C36" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C40" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4666,1082 +4719,1099 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="D12" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="D13" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="D14" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="D15" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="D16" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="R16" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="4:18">
       <c r="D17" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="4:18">
       <c r="D18" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="4:18">
       <c r="D19" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="4:18">
       <c r="D20" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="4:18">
       <c r="D21" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="4:18">
       <c r="D22" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="23" spans="4:18">
       <c r="D23" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="4:18">
       <c r="D24" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="4:18">
       <c r="D25" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="26" spans="4:18">
       <c r="D26" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="4:18">
       <c r="D27" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="4:18">
       <c r="D28" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="29" spans="4:18">
       <c r="D29" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="4:18">
       <c r="D30" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="4:18">
       <c r="D31" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32" spans="4:18">
       <c r="D32" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="14:16">
       <c r="N33" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="35" spans="14:16">
-      <c r="N35" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="O35" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="P35" s="1" t="s">
+    </row>
+    <row r="34" spans="14:16">
+      <c r="N34" s="1" t="s">
         <v>578</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="36" spans="14:16">
       <c r="N36" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="37" spans="14:16">
       <c r="N37" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="38" spans="14:16">
       <c r="N38" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="40" spans="14:16">
-      <c r="N40" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>475</v>
+        <v>587</v>
+      </c>
+    </row>
+    <row r="39" spans="14:16">
+      <c r="N39" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="41" spans="14:16">
       <c r="N41" s="1" t="s">
-        <v>585</v>
+        <v>476</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="14:16">
       <c r="N42" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>588</v>
+        <v>477</v>
       </c>
     </row>
     <row r="43" spans="14:16">
       <c r="N43" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="44" spans="14:16">
+      <c r="N44" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="45" spans="14:16">
       <c r="N45" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="46" spans="14:16">
       <c r="N46" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="14:16">
       <c r="N47" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="14:16">
       <c r="N49" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="50" spans="14:16">
       <c r="N50" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="51" spans="14:16">
       <c r="N51" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="52" spans="14:16">
       <c r="N52" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="53" spans="14:16">
       <c r="N53" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="54" spans="14:16">
       <c r="N54" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="14:16">
       <c r="N55" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -5761,64 +5831,64 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="632">
   <si>
     <t>男</t>
   </si>
@@ -699,6 +699,12 @@
     <t>（儿子）</t>
   </si>
   <si>
+    <t>証人</t>
+  </si>
+  <si>
+    <t>しょうにん</t>
+  </si>
+  <si>
     <t>次女</t>
   </si>
   <si>
@@ -712,6 +718,12 @@
   </si>
   <si>
     <t>（自家小孩）</t>
+  </si>
+  <si>
+    <t>達人</t>
+  </si>
+  <si>
+    <t>たつじん</t>
   </si>
   <si>
     <t>三女</t>
@@ -2286,9 +2298,6 @@
     <t>商人</t>
   </si>
   <si>
-    <t>しょうにん</t>
-  </si>
-  <si>
     <t>侵略者</t>
   </si>
   <si>
@@ -2355,6 +2364,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（受</t>
     </r>
     <r>
@@ -2711,14 +2726,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4243,449 +4258,461 @@
       <c r="F10" s="1" t="s">
         <v>175</v>
       </c>
+      <c r="H10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I10" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+      <c r="H11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F17" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E18" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:6">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D19" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E19" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F26" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E32" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C36" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C38" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C40" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4719,1099 +4746,1099 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="D12" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="D13" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="D14" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="D15" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="D16" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N16" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="R16" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="4:18">
       <c r="D17" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="4:18">
       <c r="D18" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="4:18">
       <c r="D19" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="4:18">
       <c r="D20" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" spans="4:18">
       <c r="D21" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="4:18">
       <c r="D22" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="4:18">
       <c r="D23" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="4:18">
       <c r="D24" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="4:18">
       <c r="D25" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="26" spans="4:18">
       <c r="D26" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" spans="4:18">
       <c r="D27" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="28" spans="4:18">
       <c r="D28" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29" spans="4:18">
       <c r="D29" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="30" spans="4:18">
       <c r="D30" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>563</v>
+        <v>177</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" spans="4:18">
       <c r="D31" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="32" spans="4:18">
       <c r="D32" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="14:16">
       <c r="N33" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="34" spans="14:16">
       <c r="N34" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36" spans="14:16">
       <c r="N36" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="37" spans="14:16">
       <c r="N37" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="38" spans="14:16">
       <c r="N38" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="39" spans="14:16">
       <c r="N39" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" spans="14:16">
       <c r="N41" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="14:16">
       <c r="N42" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="43" spans="14:16">
       <c r="N43" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="44" spans="14:16">
       <c r="N44" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="45" spans="14:16">
       <c r="N45" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="14:16">
       <c r="N46" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" spans="14:16">
       <c r="N47" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="14:16">
       <c r="N49" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="50" spans="14:16">
       <c r="N50" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="51" spans="14:16">
       <c r="N51" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="52" spans="14:16">
       <c r="N52" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="53" spans="14:16">
       <c r="N53" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="54" spans="14:16">
       <c r="N54" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="55" spans="14:16">
       <c r="N55" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -5831,64 +5858,64 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
